--- a/project-1-megapack-cost/output/megapack_cost_analysis.xlsx
+++ b/project-1-megapack-cost/output/megapack_cost_analysis.xlsx
@@ -802,7 +802,7 @@
     <row r="8" ht="46" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>Crucially this is not algebra on two numbers. The model is fitted by least squares across 24 observed prices against 3 unknowns, so it is heavily overdetermined and the residuals are a genuine test. It fits to R-squared 1.000000 with a worst residual of 0.000%, which means the decomposition is not an approximation - it recovers the pricing formula itself.</t>
+          <t>Crucially this is not algebra on two numbers. The model is fitted by least squares across 18 of the 24 observed prices - the two linear volume tiers, 3 unknowns each - so it is heavily overdetermined and the residuals are a genuine test. It fits to R-squared 1.000000 with a worst residual under 0.001%, so the decomposition is not an approximation - it recovers the pricing formula itself.</t>
         </is>
       </c>
     </row>
